--- a/reports/acdr2026_staff_deployment/参加資格マトリクス_Guest_Eligibility_Matrix_3July_整理版1006.xlsx
+++ b/reports/acdr2026_staff_deployment/参加資格マトリクス_Guest_Eligibility_Matrix_3July_整理版1006.xlsx
@@ -1909,7 +1909,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -2014,7 +2013,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>ADRCからは案内しない。一般参加者としてWeb登録すれば会議の会場には入れるが、昼食・Gala・27日の公邸レセプション・30日のサイドイベントは対象外。展示は自由。バスには乗せずタクシーを案内（10/5 宮木所長との打合せで確認。アゼルバイジャンの配偶者2名は会議に出席する意図はないと本人から聞いている）。</t>
+          <t>ADRCからは案内しない。一般参加者としてWeb登録すれば会議の会場には入れるが、昼食・Gala・30日のサイドイベントは対象外。展示は自由。27日の公邸レセプションへの入場は安達書記官の判断に任せる（児玉さん経由）。バスには乗せずタクシーを案内（10/5 宮木所長との打合せ、10/6 荒木田）。アゼルバイジャンの配偶者2名は会議に出席する意図はないと本人から聞いている。</t>
         </is>
       </c>
     </row>
